--- a/tracking_forms/033_developer_end_of_day_check_in--tracking_forms.xlsx
+++ b/tracking_forms/033_developer_end_of_day_check_in--tracking_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -744,7 +744,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Progress</t>
+          <t>Page Ten</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -767,7 +767,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Progress</t>
+          <t>Page Eleven</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -790,7 +790,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Progress</t>
+          <t>Page Twelve</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -813,7 +813,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Progress</t>
+          <t>Page Thirteen</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -836,7 +836,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Progress</t>
+          <t>Page Fourteen</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -859,7 +859,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Progress</t>
+          <t>Page Fifteen</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -882,7 +882,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Progress</t>
+          <t>Page Sixteen</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -905,7 +905,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Progress</t>
+          <t>Page Seventeen</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -928,7 +928,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Progress</t>
+          <t>Page Eighteen</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -951,7 +951,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Progress</t>
+          <t>Page Nineteen</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -974,7 +974,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Progress</t>
+          <t>Page Twenty</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -997,7 +997,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Progress</t>
+          <t>Page Twenty One</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Progress</t>
+          <t>Page Twenty Two</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1043,7 +1043,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Progress</t>
+          <t>Page Twenty Three</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Progress</t>
+          <t>Page Twenty Four</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1089,7 +1089,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Progress</t>
+          <t>Page Twenty Five</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1114,8 +1114,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1194,12 +1194,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1211,12 +1211,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
